--- a/artfynd/A 32713-2021 artfynd.xlsx
+++ b/artfynd/A 32713-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32713-2021 artfynd.xlsx
+++ b/artfynd/A 32713-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112798625</v>
+        <v>112798624</v>
       </c>
       <c r="B2" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -722,7 +717,7 @@
         <v>508399</v>
       </c>
       <c r="R2" t="n">
-        <v>6607734</v>
+        <v>6607737</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +754,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>1 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,6 +778,430 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>112798625</v>
+      </c>
+      <c r="B3" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Munkhyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>508399</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6607734</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>112798626</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Munkhyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>508372</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6607721</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>112798627</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Munkhyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>508372</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6607722</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>112798628</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Munkhyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>508356</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6607709</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
